--- a/artfynd/A 44429-2021 artfynd.xlsx
+++ b/artfynd/A 44429-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126767132</v>
       </c>
       <c r="B2" t="n">
-        <v>57459</v>
+        <v>57463</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44429-2021 artfynd.xlsx
+++ b/artfynd/A 44429-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126767132</v>
       </c>
       <c r="B2" t="n">
-        <v>57463</v>
+        <v>57465</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44429-2021 artfynd.xlsx
+++ b/artfynd/A 44429-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126767132</v>
       </c>
       <c r="B2" t="n">
-        <v>57465</v>
+        <v>57468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44429-2021 artfynd.xlsx
+++ b/artfynd/A 44429-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126767132</v>
       </c>
       <c r="B2" t="n">
-        <v>57468</v>
+        <v>57474</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44429-2021 artfynd.xlsx
+++ b/artfynd/A 44429-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126767132</v>
       </c>
       <c r="B2" t="n">
-        <v>57474</v>
+        <v>57459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44429-2021 artfynd.xlsx
+++ b/artfynd/A 44429-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,70 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126767132</v>
+        <v>111759964</v>
       </c>
       <c r="B2" t="n">
-        <v>57474</v>
+        <v>56888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102118</v>
+        <v>100041</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Hasselsnok</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Coronella austriaca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>Laurenti, 1768</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Berghäll, Boh</t>
+          <t>S:a Hamre 2:33, Gullmarn, Boh</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>296824</v>
+        <v>296724</v>
       </c>
       <c r="R2" t="n">
-        <v>6471343</v>
+        <v>6471306</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,12 +765,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2023-08-19</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-18</t>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Solande, troligtvis hona ca 60 cm lång, återkommande vid soligt väder.  Efter bildanalys av Naturhistoriskas ormexpert är det en snok ytterligare på bild en av fynddagarna, troligtvis en hane med ljusare skinn. Fynd på tomtgräns Hamre 2:33 mot stamfastighet 2:5 skogsområde.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,6 +794,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,6 +810,349 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>109949064</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S:a Hamre 2:33, Gullmarn, Boh</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>296724</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6471306</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lysekil</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lyse</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spillkråka strimlat stubbe på tomt S:a Hamre 140 Lysekil Foto på stubbe finns, fågel hann lyfta...</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Göran Hamrefors</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Göran Hamrefors</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118470733</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S:a Hamre 2:33, Gullmarn, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>296724</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6471306</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lysekil</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lyse</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spelsång samt vingslag</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Göran Hamrefors</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Göran Hamrefors</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126767132</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Berghäll, Boh</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>296824</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6471343</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lysekil</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lyse</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Göran Hamrefors</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Göran Hamrefors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44429-2021 artfynd.xlsx
+++ b/artfynd/A 44429-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -810,6 +815,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111759964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109949064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1048,6 +1063,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118470733</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1153,8 +1173,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126767132</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>